--- a/Result/profitability/6210.xlsx
+++ b/Result/profitability/6210.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.65</v>
+        <v>-0.5575</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.00375</v>
+        <v>-12.815</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4225</v>
+        <v>-0.32875</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.84375</v>
+        <v>-5.31</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2487500000000001</v>
+        <v>-0.17625</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.17125</v>
+        <v>0.3987499999999997</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1425000000000001</v>
+        <v>-0.03000000000000005</v>
       </c>
       <c r="N5" t="n">
-        <v>2.06</v>
+        <v>7.3325</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.122502256758253e-17</v>
+        <v>0.08499999999999995</v>
       </c>
       <c r="N6" t="n">
-        <v>8.97875</v>
+        <v>12.89125</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09749999999999998</v>
+        <v>0.1099999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>15.14125</v>
+        <v>15.9325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20875</v>
+        <v>0.23375</v>
       </c>
       <c r="N8" t="n">
-        <v>18.98375</v>
+        <v>19.76</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3775</v>
+        <v>0.3774999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>23.24875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>109</v>
+      </c>
+      <c r="D75" t="n">
+        <v>104</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.7037500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-17.365</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4878048780487805</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-4.058823529411764</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8108108108108109</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.1248</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
